--- a/artfynd/A 56412-2025 artfynd.xlsx
+++ b/artfynd/A 56412-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116935919</v>
+        <v>101236069</v>
       </c>
       <c r="B2" t="n">
-        <v>79550</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barsele, Ly lm</t>
+          <t>Västervik, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622211</v>
+        <v>622086</v>
       </c>
       <c r="R2" t="n">
-        <v>7213698</v>
+        <v>7213660</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,78 +761,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Bäckmiljö</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Jörgen Olsson</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Jörgen Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Jörgen Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116935924</v>
+        <v>101236066</v>
       </c>
       <c r="B3" t="n">
-        <v>79550</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barsele, Ly lm</t>
+          <t>Västervik, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622229</v>
+        <v>622086</v>
       </c>
       <c r="R3" t="n">
-        <v>7213687</v>
+        <v>7213660</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,38 +866,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Jörgen Olsson</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Jörgen Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Jörgen Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116935925</v>
+        <v>116935919</v>
       </c>
       <c r="B4" t="n">
-        <v>79557</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622229</v>
+        <v>622211</v>
       </c>
       <c r="R4" t="n">
-        <v>7213687</v>
+        <v>7213698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,6 +966,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bäckmiljö</t>
+        </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1001,15 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116935926</v>
+        <v>116935924</v>
       </c>
       <c r="B5" t="n">
-        <v>79556</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1003,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1108,15 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116935927</v>
+        <v>101236071</v>
       </c>
       <c r="B6" t="n">
-        <v>57637</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1105,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barsele, Ly lm</t>
+          <t>Västervik, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622384</v>
+        <v>622086</v>
       </c>
       <c r="R6" t="n">
-        <v>7213550</v>
+        <v>7213660</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,38 +1180,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Jörgen Olsson</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Jörgen Olsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Jörgen Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116935920</v>
+        <v>116935926</v>
       </c>
       <c r="B7" t="n">
-        <v>79557</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622211</v>
+        <v>622229</v>
       </c>
       <c r="R7" t="n">
-        <v>7213698</v>
+        <v>7213687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,11 +1280,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Bäckmiljö</t>
-        </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -1327,55 +1301,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121561232</v>
+        <v>101236072</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Västervik, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622289</v>
+        <v>622086</v>
       </c>
       <c r="R8" t="n">
-        <v>7213497</v>
+        <v>7213660</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,12 +1373,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2018-06-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2018-06-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,73 +1387,64 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Jörgen Olsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Jörgen Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121561233</v>
+        <v>116935920</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Barsele, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622306</v>
+        <v>622211</v>
       </c>
       <c r="R9" t="n">
-        <v>7213443</v>
+        <v>7213698</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,12 +1471,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2018-06-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2018-06-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,19 +1487,1039 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>116935925</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Barsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>622229</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7213687</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-06-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-06-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110541214</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SO Skirträsket, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>622082</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7213642</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-06-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-06-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Via Isak Vahlström</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121561227</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>622269</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7213610</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121561232</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>622289</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7213497</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121561233</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>622306</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7213443</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121561234</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>622337</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7213406</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120718960</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Västervik, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>622364</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7213409</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120718964</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Västervik, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>622404</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7213458</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121561217</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>622711</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7213756</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>116935927</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Barsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>622384</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7213550</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2018-06-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2018-06-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
